--- a/Team-Data/2014-15/3-28-2014-15.xlsx
+++ b/Team-Data/2014-15/3-28-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" t="n">
         <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>0.753</v>
+        <v>0.764</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -685,19 +752,19 @@
         <v>0.465</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M2" t="n">
         <v>25.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="O2" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P2" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q2" t="n">
         <v>0.779</v>
@@ -706,13 +773,13 @@
         <v>8.6</v>
       </c>
       <c r="S2" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T2" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U2" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="V2" t="n">
         <v>14.4</v>
@@ -736,10 +803,10 @@
         <v>102.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -751,7 +818,7 @@
         <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -763,7 +830,7 @@
         <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM2" t="n">
         <v>7</v>
@@ -772,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
@@ -808,13 +875,13 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>18</v>
@@ -933,7 +1000,7 @@
         <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
         <v>6</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
@@ -981,16 +1048,16 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
         <v>23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
         <v>14</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -1103,16 +1170,16 @@
         <v>-3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1121,7 +1188,7 @@
         <v>19</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
         <v>16</v>
@@ -1148,16 +1215,16 @@
         <v>24</v>
       </c>
       <c r="AS4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT4" t="n">
         <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1274,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.431</v>
+        <v>0.423</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J5" t="n">
         <v>84.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.423</v>
+        <v>0.422</v>
       </c>
       <c r="L5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.318</v>
+        <v>0.315</v>
       </c>
       <c r="O5" t="n">
         <v>17.3</v>
@@ -1246,7 +1313,7 @@
         <v>23.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
@@ -1258,13 +1325,13 @@
         <v>44.4</v>
       </c>
       <c r="U5" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V5" t="n">
         <v>11.9</v>
       </c>
       <c r="W5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
@@ -1276,28 +1343,28 @@
         <v>18.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>95</v>
+        <v>94.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
         <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1324,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1336,22 +1403,22 @@
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
         <v>7</v>
@@ -1360,7 +1427,7 @@
         <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>0.608</v>
+        <v>0.603</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1410,7 +1477,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L6" t="n">
         <v>7.8</v>
@@ -1425,34 +1492,34 @@
         <v>19.8</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R6" t="n">
         <v>11.7</v>
       </c>
       <c r="S6" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T6" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="U6" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V6" t="n">
         <v>13.9</v>
       </c>
       <c r="W6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="X6" t="n">
         <v>5.9</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z6" t="n">
         <v>18.4</v>
@@ -1461,16 +1528,16 @@
         <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.1</v>
+        <v>101</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1479,10 +1546,10 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
         <v>17</v>
@@ -1518,31 +1585,31 @@
         <v>3</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX6" t="n">
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
         <v>13</v>
       </c>
       <c r="BC6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -1658,19 +1725,19 @@
         <v>8</v>
       </c>
       <c r="AG7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,7 +1746,7 @@
         <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1694,28 +1761,28 @@
         <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT7" t="n">
         <v>19</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
         <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.625</v>
+        <v>0.616</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,16 +1838,16 @@
         <v>39.3</v>
       </c>
       <c r="J8" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="N8" t="n">
         <v>0.352</v>
@@ -1792,22 +1859,22 @@
         <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R8" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="W8" t="n">
         <v>8.300000000000001</v>
@@ -1816,7 +1883,7 @@
         <v>4.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z8" t="n">
         <v>19.8</v>
@@ -1825,25 +1892,25 @@
         <v>21.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1852,7 +1919,7 @@
         <v>9</v>
       </c>
       <c r="AK8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
@@ -1861,7 +1928,7 @@
         <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
         <v>21</v>
@@ -1873,16 +1940,16 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
         <v>28</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>0.378</v>
+        <v>0.384</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J9" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L9" t="n">
         <v>7.9</v>
@@ -1965,16 +2032,16 @@
         <v>24.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O9" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P9" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="R9" t="n">
         <v>12.1</v>
@@ -1983,16 +2050,16 @@
         <v>32.6</v>
       </c>
       <c r="T9" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U9" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V9" t="n">
         <v>14.2</v>
       </c>
       <c r="W9" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X9" t="n">
         <v>4.7</v>
@@ -2001,19 +2068,19 @@
         <v>6.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC9" t="n">
         <v>-3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,10 +2092,10 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI9" t="n">
         <v>18</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>17</v>
       </c>
       <c r="AJ9" t="n">
         <v>3</v>
@@ -2046,10 +2113,10 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2067,7 +2134,7 @@
         <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2213,7 +2280,7 @@
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.822</v>
+        <v>0.819</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
@@ -2317,7 +2384,7 @@
         <v>41.5</v>
       </c>
       <c r="J11" t="n">
-        <v>86.7</v>
+        <v>86.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.478</v>
@@ -2329,7 +2396,7 @@
         <v>27.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.397</v>
+        <v>0.396</v>
       </c>
       <c r="O11" t="n">
         <v>16.1</v>
@@ -2338,13 +2405,13 @@
         <v>20.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R11" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S11" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="T11" t="n">
         <v>44.6</v>
@@ -2353,13 +2420,13 @@
         <v>27.4</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W11" t="n">
         <v>9.5</v>
       </c>
       <c r="X11" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y11" t="n">
         <v>3.4</v>
@@ -2377,7 +2444,7 @@
         <v>10.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2410,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>26</v>
@@ -2434,10 +2501,10 @@
         <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -2481,52 +2548,52 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
         <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0.676</v>
+        <v>0.681</v>
       </c>
       <c r="H12" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J12" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L12" t="n">
         <v>11.5</v>
       </c>
       <c r="M12" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O12" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P12" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T12" t="n">
         <v>43.5</v>
@@ -2547,19 +2614,19 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2589,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>26</v>
@@ -2610,31 +2677,31 @@
         <v>17</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -2741,19 +2808,19 @@
         <v>-0.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
         <v>20</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2771,16 +2838,16 @@
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>17</v>
       </c>
       <c r="AP13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
         <v>21</v>
@@ -2807,16 +2874,16 @@
         <v>16</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>6.2</v>
       </c>
       <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
         <v>5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2935,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2947,7 +3014,7 @@
         <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
         <v>5</v>
@@ -2956,7 +3023,7 @@
         <v>3</v>
       </c>
       <c r="AO14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
         <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>0.271</v>
+        <v>0.268</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M15" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N15" t="n">
         <v>0.342</v>
       </c>
       <c r="O15" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P15" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
         <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3093,19 +3160,19 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.7</v>
+        <v>-5.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3120,7 +3187,7 @@
         <v>4</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
@@ -3135,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP15" t="n">
         <v>12</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>13</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3150,13 +3217,13 @@
         <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
         <v>11</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV15" t="n">
         <v>5</v>
@@ -3174,7 +3241,7 @@
         <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3302,7 +3369,7 @@
         <v>6</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ16" t="n">
         <v>21</v>
@@ -3320,7 +3387,7 @@
         <v>16</v>
       </c>
       <c r="AO16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP16" t="n">
         <v>15</v>
@@ -3332,7 +3399,7 @@
         <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
         <v>20</v>
@@ -3350,10 +3417,10 @@
         <v>24</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>14</v>
@@ -3362,7 +3429,7 @@
         <v>18</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3523,7 +3590,7 @@
         <v>28</v>
       </c>
       <c r="AV17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW17" t="n">
         <v>10</v>
@@ -3544,7 +3611,7 @@
         <v>28</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" t="n">
         <v>36</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>48.7</v>
@@ -3591,34 +3658,34 @@
         <v>37.4</v>
       </c>
       <c r="J18" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M18" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.366</v>
+        <v>0.369</v>
       </c>
       <c r="O18" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P18" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R18" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S18" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T18" t="n">
         <v>42.1</v>
@@ -3630,13 +3697,13 @@
         <v>16.8</v>
       </c>
       <c r="W18" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X18" t="n">
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z18" t="n">
         <v>22.2</v>
@@ -3648,10 +3715,10 @@
         <v>97.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3666,22 +3733,22 @@
         <v>3</v>
       </c>
       <c r="AI18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
         <v>26</v>
       </c>
       <c r="AK18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM18" t="n">
         <v>26</v>
       </c>
       <c r="AN18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
@@ -3690,34 +3757,34 @@
         <v>25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
         <v>9</v>
       </c>
       <c r="AY18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-7.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,13 +3912,13 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK19" t="n">
         <v>23</v>
@@ -3875,7 +3942,7 @@
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3884,7 +3951,7 @@
         <v>25</v>
       </c>
       <c r="AU19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F20" t="n">
         <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>0.521</v>
+        <v>0.528</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,70 +4022,70 @@
         <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>7.1</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="O20" t="n">
         <v>16.5</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
         <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W20" t="n">
         <v>6.7</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z20" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AA20" t="n">
         <v>18.7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>18.6</v>
       </c>
       <c r="AB20" t="n">
         <v>99.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
@@ -4030,13 +4097,13 @@
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4045,28 +4112,28 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
         <v>20</v>
       </c>
       <c r="AP20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>10</v>
       </c>
       <c r="AS20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4084,13 +4151,13 @@
         <v>6</v>
       </c>
       <c r="BA20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -4119,22 +4186,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>0.189</v>
+        <v>0.192</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J21" t="n">
         <v>82.40000000000001</v>
@@ -4149,7 +4216,7 @@
         <v>19.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O21" t="n">
         <v>14.5</v>
@@ -4158,22 +4225,22 @@
         <v>18.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R21" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U21" t="n">
         <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
@@ -4185,19 +4252,19 @@
         <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA21" t="n">
         <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>30</v>
@@ -4212,7 +4279,7 @@
         <v>13</v>
       </c>
       <c r="AI21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ21" t="n">
         <v>23</v>
@@ -4221,7 +4288,7 @@
         <v>27</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
         <v>41</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J22" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.447</v>
@@ -4328,19 +4395,19 @@
         <v>7.5</v>
       </c>
       <c r="M22" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.336</v>
+        <v>0.335</v>
       </c>
       <c r="O22" t="n">
         <v>18.6</v>
       </c>
       <c r="P22" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R22" t="n">
         <v>12.6</v>
@@ -4352,10 +4419,10 @@
         <v>47.5</v>
       </c>
       <c r="U22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V22" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W22" t="n">
         <v>7.3</v>
@@ -4367,19 +4434,19 @@
         <v>4.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.2</v>
+        <v>103.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>12</v>
@@ -4391,13 +4458,13 @@
         <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
@@ -4418,7 +4485,7 @@
         <v>8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4430,13 +4497,13 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
         <v>6</v>
@@ -4445,16 +4512,16 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB22" t="n">
         <v>8</v>
       </c>
       <c r="BC22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>0.301</v>
+        <v>0.297</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J23" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>6.8</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
         <v>0.35</v>
@@ -4519,22 +4586,22 @@
         <v>14.1</v>
       </c>
       <c r="P23" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U23" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4546,22 +4613,22 @@
         <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4585,7 +4652,7 @@
         <v>12</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4606,28 +4673,28 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
       </c>
       <c r="AU23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV23" t="n">
         <v>22</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>20</v>
       </c>
       <c r="AW23" t="n">
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4794,7 +4861,7 @@
         <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4943,7 +5010,7 @@
         <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
         <v>13</v>
@@ -4955,22 +5022,22 @@
         <v>9</v>
       </c>
       <c r="AN25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO25" t="n">
         <v>19</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT25" t="n">
         <v>15</v>
@@ -4985,7 +5052,7 @@
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F26" t="n">
         <v>25</v>
       </c>
       <c r="G26" t="n">
-        <v>0.653</v>
+        <v>0.648</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J26" t="n">
         <v>85.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L26" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O26" t="n">
         <v>15.8</v>
@@ -5068,7 +5135,7 @@
         <v>19.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R26" t="n">
         <v>10.8</v>
@@ -5080,10 +5147,10 @@
         <v>45.9</v>
       </c>
       <c r="U26" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V26" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W26" t="n">
         <v>6.5</v>
@@ -5092,7 +5159,7 @@
         <v>4.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
         <v>18.3</v>
@@ -5101,16 +5168,16 @@
         <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.5</v>
+        <v>102.3</v>
       </c>
       <c r="AC26" t="n">
         <v>4.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5128,10 +5195,10 @@
         <v>8</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
         <v>2</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5179,7 +5246,7 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F28" t="n">
         <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>0.634</v>
+        <v>0.639</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,49 +5478,49 @@
         <v>38.7</v>
       </c>
       <c r="J28" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K28" t="n">
         <v>0.462</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.364</v>
+        <v>0.366</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.776</v>
+        <v>0.777</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U28" t="n">
         <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W28" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
         <v>4.5</v>
@@ -5468,19 +5535,19 @@
         <v>102.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF28" t="n">
         <v>7</v>
       </c>
       <c r="AG28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK28" t="n">
         <v>5</v>
@@ -5501,13 +5568,13 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>6</v>
@@ -5519,13 +5586,13 @@
         <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>4</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
         <v>12</v>
@@ -5546,7 +5613,7 @@
         <v>9</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5683,7 +5750,7 @@
         <v>11</v>
       </c>
       <c r="AN29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
@@ -5695,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5722,7 +5789,7 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -5757,64 +5824,64 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F30" t="n">
         <v>41</v>
       </c>
       <c r="G30" t="n">
-        <v>0.438</v>
+        <v>0.431</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J30" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L30" t="n">
         <v>7.3</v>
       </c>
       <c r="M30" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.341</v>
+        <v>0.344</v>
       </c>
       <c r="O30" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P30" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="R30" t="n">
         <v>11.9</v>
       </c>
       <c r="S30" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T30" t="n">
         <v>43.7</v>
       </c>
       <c r="U30" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
         <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X30" t="n">
         <v>6</v>
@@ -5823,40 +5890,40 @@
         <v>4.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AB30" t="n">
         <v>94.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF30" t="n">
         <v>20</v>
       </c>
       <c r="AG30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
         <v>17</v>
@@ -5865,52 +5932,52 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ30" t="n">
         <v>27</v>
       </c>
       <c r="AR30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV30" t="n">
         <v>25</v>
       </c>
       <c r="AW30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
         <v>12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
       </c>
       <c r="BC30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>0.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
         <v>7</v>
@@ -6074,7 +6141,7 @@
         <v>20</v>
       </c>
       <c r="AW31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-28-2014-15</t>
+          <t>2015-03-28</t>
         </is>
       </c>
     </row>
